--- a/Data/Poverty/Poverty by Province.xlsx
+++ b/Data/Poverty/Poverty by Province.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AJ\GitHub Repositories\PH-Econ-Data\Data\Poverty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72A19D2-15E9-470D-930C-E088E14CCF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034E75F1-36AF-4FFA-B062-FC037388A300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{354455D8-F3A3-48D2-BFDA-2EC7AC494458}"/>
+    <workbookView xWindow="8175" yWindow="1185" windowWidth="14715" windowHeight="13245" xr2:uid="{354455D8-F3A3-48D2-BFDA-2EC7AC494458}"/>
   </bookViews>
   <sheets>
-    <sheet name="2015-2021" sheetId="1" r:id="rId1"/>
+    <sheet name="2015-2023" sheetId="1" r:id="rId1"/>
     <sheet name="2006-2015" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
